--- a/data/trans_orig/P57C1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57C1_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha sido optimista respecto a su futuro en 2023</t>
+          <t>Población según si ha sido optimista respecto a su futuro en 2023 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20799</t>
+          <t>18657</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25733</t>
+          <t>24169</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23000</t>
+          <t>23468</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7391</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17691</t>
+          <t>18503</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17592</t>
+          <t>17830</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36077</t>
+          <t>35918</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43197</t>
+          <t>42542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>70724</t>
+          <t>69537</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31143</t>
+          <t>30499</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53671</t>
+          <t>52370</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>79675</t>
+          <t>80431</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>113321</t>
+          <t>113810</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>228393</t>
+          <t>230152</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>274889</t>
+          <t>278128</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>180098</t>
+          <t>181583</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>216655</t>
+          <t>216729</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>419960</t>
+          <t>422782</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>482375</t>
+          <t>482523</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,65%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>153481</t>
+          <t>151420</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>198501</t>
+          <t>195328</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>175003</t>
+          <t>173967</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>210673</t>
+          <t>209493</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>337740</t>
+          <t>338589</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>396925</t>
+          <t>393709</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,33%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>779</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6704</t>
+          <t>6703</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11458</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11099</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29973</t>
+          <t>29297</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10916</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24080</t>
+          <t>23429</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25533</t>
+          <t>25236</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48931</t>
+          <t>47033</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37126</t>
+          <t>36741</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61030</t>
+          <t>61587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30287</t>
+          <t>30039</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49457</t>
+          <t>49249</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>72175</t>
+          <t>71418</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>103020</t>
+          <t>103041</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>192438</t>
+          <t>188973</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>235597</t>
+          <t>234174</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>169893</t>
+          <t>168198</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>201457</t>
+          <t>201726</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>369623</t>
+          <t>371350</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>425019</t>
+          <t>427211</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,18%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148445</t>
+          <t>149810</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>191769</t>
+          <t>195089</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>122718</t>
+          <t>122938</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>153738</t>
+          <t>155896</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>281613</t>
+          <t>279372</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>337181</t>
+          <t>334127</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,03%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20036</t>
+          <t>20336</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>299</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>5794</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21501</t>
+          <t>21016</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>7433</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38840</t>
+          <t>38900</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7942</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18607</t>
+          <t>18273</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>13839</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53143</t>
+          <t>53203</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17269</t>
+          <t>14942</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79456</t>
+          <t>81040</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37486</t>
+          <t>37702</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30922</t>
+          <t>29510</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>114575</t>
+          <t>111902</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77696</t>
+          <t>80946</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>334339</t>
+          <t>333860</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66098</t>
+          <t>64740</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86219</t>
+          <t>85334</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>120696</t>
+          <t>116733</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>405512</t>
+          <t>407644</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,87%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>212020</t>
+          <t>213224</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>558652</t>
+          <t>553137</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38541</t>
+          <t>38078</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57370</t>
+          <t>58353</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>254070</t>
+          <t>256294</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>660446</t>
+          <t>668304</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>80,12%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13984</t>
+          <t>14394</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32143</t>
+          <t>32165</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7537</t>
+          <t>7196</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23786</t>
+          <t>24357</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24323</t>
+          <t>25225</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49688</t>
+          <t>50249</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>53884</t>
+          <t>51232</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>82433</t>
+          <t>81927</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20407</t>
+          <t>16863</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>51517</t>
+          <t>51820</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>73607</t>
+          <t>75203</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>127337</t>
+          <t>126953</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>113417</t>
+          <t>114809</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>160411</t>
+          <t>159498</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52678</t>
+          <t>47203</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>132892</t>
+          <t>131871</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>158817</t>
+          <t>158953</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>270081</t>
+          <t>274173</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>438074</t>
+          <t>440556</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>509202</t>
+          <t>511836</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>480374</t>
+          <t>481237</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>761109</t>
+          <t>772604</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>944142</t>
+          <t>947159</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1361214</t>
+          <t>1357166</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,59%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>299249</t>
+          <t>299530</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>369465</t>
+          <t>373188</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>126278</t>
+          <t>127236</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>302173</t>
+          <t>301217</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>389618</t>
+          <t>391513</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>646789</t>
+          <t>643210</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12241</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>28281</t>
+          <t>28484</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27925</t>
+          <t>27693</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>52520</t>
+          <t>51654</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>43764</t>
+          <t>43367</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>74608</t>
+          <t>74030</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29134</t>
+          <t>29660</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>51409</t>
+          <t>51945</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>54965</t>
+          <t>54308</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>90001</t>
+          <t>89983</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>90055</t>
+          <t>91109</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>134273</t>
+          <t>131920</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>65960</t>
+          <t>66058</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>97059</t>
+          <t>98637</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>106243</t>
+          <t>107457</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>165098</t>
+          <t>164846</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>251574</t>
+          <t>251662</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,2%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>176256</t>
+          <t>175414</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>221573</t>
+          <t>221085</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>258095</t>
+          <t>246949</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>388254</t>
+          <t>385251</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>448055</t>
+          <t>436238</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>593941</t>
+          <t>590862</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,08%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>117841</t>
+          <t>114994</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>160469</t>
+          <t>159810</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>187657</t>
+          <t>186993</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>397573</t>
+          <t>408033</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>322826</t>
+          <t>324139</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>569111</t>
+          <t>560474</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>42,76%</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>11611</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>26807</t>
+          <t>26831</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>13371</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>29723</t>
+          <t>27848</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>508</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>56330</t>
+          <t>56517</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>86217</t>
+          <t>85679</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>57796</t>
+          <t>58437</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>89142</t>
+          <t>90781</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9800</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>35364</t>
+          <t>35633</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>136587</t>
+          <t>136516</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>175978</t>
+          <t>174287</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>152107</t>
+          <t>154243</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>201004</t>
+          <t>202442</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>65413</t>
+          <t>65786</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>118802</t>
+          <t>116675</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>276046</t>
+          <t>272596</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>324092</t>
+          <t>324268</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>353331</t>
+          <t>353611</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>425840</t>
+          <t>426683</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,77%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>100224</t>
+          <t>98831</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>154019</t>
+          <t>151330</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>194096</t>
+          <t>192525</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>242812</t>
+          <t>242280</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>307583</t>
+          <t>310037</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>382228</t>
+          <t>384816</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,57%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>45818</t>
+          <t>46788</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>81312</t>
+          <t>82685</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>66142</t>
+          <t>66127</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>102293</t>
+          <t>98320</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>118697</t>
+          <t>121994</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>172341</t>
+          <t>170593</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>126742</t>
+          <t>119041</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>189992</t>
+          <t>188750</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>181240</t>
+          <t>177079</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>251901</t>
+          <t>250805</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>330346</t>
+          <t>330528</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>428377</t>
+          <t>429529</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>306472</t>
+          <t>292888</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>435413</t>
+          <t>431818</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>416656</t>
+          <t>411228</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>555856</t>
+          <t>554448</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>756816</t>
+          <t>780547</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>968522</t>
+          <t>969948</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1096171</t>
+          <t>1065398</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1564666</t>
+          <t>1569717</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1535122</t>
+          <t>1525327</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>2038507</t>
+          <t>2052009</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2769059</t>
+          <t>2827341</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3419225</t>
+          <t>3464633</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,94%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1148956</t>
+          <t>1147325</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1782563</t>
+          <t>1873387</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>895253</t>
+          <t>891628</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1211237</t>
+          <t>1227063</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2173677</t>
+          <t>2147257</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2994417</t>
+          <t>2933099</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>42,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57C1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57C1_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9885</t>
+          <t>10938</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18657</t>
+          <t>22436</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4342</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8851</t>
+          <t>9284</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,17 +795,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14227</t>
+          <t>15433</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7800</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24169</t>
+          <t>26884</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13466</t>
+          <t>13991</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7660</t>
+          <t>7777</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23468</t>
+          <t>23640</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11915</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>9668</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18503</t>
+          <t>25033</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>25381</t>
+          <t>29136</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17830</t>
+          <t>20079</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35918</t>
+          <t>41854</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>54633</t>
+          <t>59592</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42542</t>
+          <t>47566</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69537</t>
+          <t>75873</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>41091</t>
+          <t>45426</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30499</t>
+          <t>35250</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52370</t>
+          <t>59428</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>95725</t>
+          <t>105019</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>80431</t>
+          <t>88487</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>113810</t>
+          <t>127128</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>252918</t>
+          <t>268080</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>230152</t>
+          <t>245095</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>278128</t>
+          <t>294464</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>198975</t>
+          <t>213743</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>181583</t>
+          <t>194613</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>216729</t>
+          <t>234566</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>451893</t>
+          <t>481823</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>422782</t>
+          <t>448900</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>482523</t>
+          <t>511215</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>49,2%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>174310</t>
+          <t>198016</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>151420</t>
+          <t>173500</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>195328</t>
+          <t>220794</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>191143</t>
+          <t>209602</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>173967</t>
+          <t>189165</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>209493</t>
+          <t>229455</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>365454</t>
+          <t>407618</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>338589</t>
+          <t>378186</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>393709</t>
+          <t>439514</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6703</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>4539</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>9288</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6495</t>
+          <t>7597</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>13665</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17733</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29297</t>
+          <t>29402</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16852</t>
+          <t>18278</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11061</t>
+          <t>12326</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>26673</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,22 +1590,22 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>34584</t>
+          <t>36115</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25236</t>
+          <t>27365</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47033</t>
+          <t>49581</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48431</t>
+          <t>51455</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36741</t>
+          <t>40109</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61587</t>
+          <t>64941</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>38899</t>
+          <t>42411</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30039</t>
+          <t>33366</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49249</t>
+          <t>53307</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>87330</t>
+          <t>93867</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>71418</t>
+          <t>78714</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>103041</t>
+          <t>111434</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>213343</t>
+          <t>226720</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>188973</t>
+          <t>202887</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>234174</t>
+          <t>249188</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>184945</t>
+          <t>201750</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>168198</t>
+          <t>184131</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>201726</t>
+          <t>221375</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>398289</t>
+          <t>428469</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>371350</t>
+          <t>398652</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>427211</t>
+          <t>457255</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>50,45%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>169986</t>
+          <t>184142</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149810</t>
+          <t>163728</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>195089</t>
+          <t>210112</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>138109</t>
+          <t>156164</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>122938</t>
+          <t>138729</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155896</t>
+          <t>173821</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>308095</t>
+          <t>340307</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>279372</t>
+          <t>312958</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>334127</t>
+          <t>368846</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,7%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20336</t>
+          <t>19904</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>283</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>5137</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>11531</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21016</t>
+          <t>20953</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21849</t>
+          <t>23020</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>15825</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38900</t>
+          <t>32341</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12617</t>
+          <t>13790</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18273</t>
+          <t>20582</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>34465</t>
+          <t>36810</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13839</t>
+          <t>27067</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53203</t>
+          <t>47660</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>47416</t>
+          <t>49699</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14942</t>
+          <t>38531</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81040</t>
+          <t>62420</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29328</t>
+          <t>31566</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>24695</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37702</t>
+          <t>41395</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>76744</t>
+          <t>81265</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>29510</t>
+          <t>68009</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>111902</t>
+          <t>97035</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>204860</t>
+          <t>227689</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>80946</t>
+          <t>205642</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>333860</t>
+          <t>250064</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>75907</t>
+          <t>83015</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>64740</t>
+          <t>71797</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85334</t>
+          <t>94527</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>280767</t>
+          <t>310704</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116733</t>
+          <t>284744</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>407644</t>
+          <t>337859</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>51,33%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>383404</t>
+          <t>160438</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>213224</t>
+          <t>136085</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>553137</t>
+          <t>182879</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>47383</t>
+          <t>57426</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38078</t>
+          <t>47144</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58353</t>
+          <t>69799</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>430787</t>
+          <t>217864</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>256294</t>
+          <t>192246</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>668304</t>
+          <t>240646</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>36,56%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>667259</t>
+          <t>470677</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>667259</t>
+          <t>470677</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>667259</t>
+          <t>470677</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>834170</t>
+          <t>658175</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>834170</t>
+          <t>658175</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>834170</t>
+          <t>658175</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>21517</t>
+          <t>22618</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14394</t>
+          <t>14994</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32165</t>
+          <t>33825</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>15717</t>
+          <t>17080</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24357</t>
+          <t>25482</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>37235</t>
+          <t>39698</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25225</t>
+          <t>28736</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50249</t>
+          <t>52185</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>66925</t>
+          <t>70046</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>51232</t>
+          <t>57749</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>81927</t>
+          <t>86615</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>37626</t>
+          <t>43355</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>16863</t>
+          <t>34999</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>51820</t>
+          <t>55819</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>104550</t>
+          <t>113401</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>75203</t>
+          <t>95660</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>126953</t>
+          <t>134266</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>134968</t>
+          <t>147198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>114809</t>
+          <t>126882</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>159498</t>
+          <t>173770</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>99612</t>
+          <t>109916</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>47203</t>
+          <t>94078</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>131871</t>
+          <t>126183</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>234580</t>
+          <t>257114</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>158953</t>
+          <t>230621</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>274173</t>
+          <t>286378</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>474513</t>
+          <t>522877</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>440556</t>
+          <t>487548</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>511836</t>
+          <t>560994</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>591043</t>
+          <t>424234</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>481237</t>
+          <t>398156</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>772604</t>
+          <t>447724</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1065556</t>
+          <t>947111</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>947159</t>
+          <t>907841</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1357166</t>
+          <t>995213</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>50,07%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>334798</t>
+          <t>366762</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>299530</t>
+          <t>330232</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>373188</t>
+          <t>403675</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>231198</t>
+          <t>263700</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>127236</t>
+          <t>241370</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>301217</t>
+          <t>288912</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>565996</t>
+          <t>630461</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>391513</t>
+          <t>585082</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>643210</t>
+          <t>672039</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>33,81%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1032721</t>
+          <t>1129500</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1032721</t>
+          <t>1129500</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1032721</t>
+          <t>1129500</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>975195</t>
+          <t>858285</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>975195</t>
+          <t>858285</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>975195</t>
+          <t>858285</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2007916</t>
+          <t>1987784</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2007916</t>
+          <t>1987784</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2007916</t>
+          <t>1987784</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>18633</t>
+          <t>23025</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>14980</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>28484</t>
+          <t>33131</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>38868</t>
+          <t>42325</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27693</t>
+          <t>33743</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>51654</t>
+          <t>57993</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>57502</t>
+          <t>65350</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>43367</t>
+          <t>53183</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>74030</t>
+          <t>82340</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>39011</t>
+          <t>42561</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29660</t>
+          <t>32358</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>51945</t>
+          <t>55303</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>74012</t>
+          <t>82245</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>54308</t>
+          <t>68519</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>89983</t>
+          <t>96046</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>113023</t>
+          <t>124806</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>91109</t>
+          <t>108843</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>131920</t>
+          <t>144887</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>80652</t>
+          <t>97024</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>66058</t>
+          <t>81036</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>98637</t>
+          <t>118330</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>141639</t>
+          <t>161413</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>107457</t>
+          <t>145666</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>164846</t>
+          <t>181296</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>222292</t>
+          <t>258437</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>181477</t>
+          <t>232982</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>251662</t>
+          <t>285741</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>198030</t>
+          <t>230518</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>175414</t>
+          <t>205562</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>221085</t>
+          <t>256048</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>332005</t>
+          <t>342660</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>246949</t>
+          <t>318990</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>385251</t>
+          <t>365865</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>530035</t>
+          <t>573177</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>436238</t>
+          <t>538025</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>590862</t>
+          <t>607826</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>137155</t>
+          <t>173316</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>114994</t>
+          <t>146753</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>159810</t>
+          <t>197087</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>250817</t>
+          <t>196484</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>186993</t>
+          <t>176690</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>408033</t>
+          <t>218008</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>387972</t>
+          <t>369800</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>324139</t>
+          <t>336336</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>560474</t>
+          <t>404824</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>473482</t>
+          <t>566443</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>473482</t>
+          <t>566443</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>473482</t>
+          <t>566443</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>837341</t>
+          <t>825127</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>837341</t>
+          <t>825127</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>837341</t>
+          <t>825127</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1310823</t>
+          <t>1391570</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1310823</t>
+          <t>1391570</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1310823</t>
+          <t>1391570</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4160,42 +4160,42 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>18218</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>12186</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>28001</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
           <t>2,17%</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>17530</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>11648</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>26831</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>18992</t>
+          <t>19693</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>12919</t>
+          <t>13388</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>27848</t>
+          <t>28932</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>523</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>9223</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>68479</t>
+          <t>73403</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>56517</t>
+          <t>61229</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>85679</t>
+          <t>88406</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>71008</t>
+          <t>76023</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>58437</t>
+          <t>63237</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>90781</t>
+          <t>93624</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>19753</t>
+          <t>19144</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>35633</t>
+          <t>33448</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>154560</t>
+          <t>169930</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>136516</t>
+          <t>149338</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>174287</t>
+          <t>190807</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>174313</t>
+          <t>189074</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>154243</t>
+          <t>166105</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>202442</t>
+          <t>214108</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>89940</t>
+          <t>79857</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>65786</t>
+          <t>60645</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>116675</t>
+          <t>104758</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>299814</t>
+          <t>340882</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>272596</t>
+          <t>312601</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>324268</t>
+          <t>366201</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>389754</t>
+          <t>420739</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>353611</t>
+          <t>387227</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>426683</t>
+          <t>456843</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,44%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>126823</t>
+          <t>134132</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>98831</t>
+          <t>106592</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>151330</t>
+          <t>155011</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>216767</t>
+          <t>236767</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>192525</t>
+          <t>212305</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>242280</t>
+          <t>266743</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>343590</t>
+          <t>370899</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>310037</t>
+          <t>334911</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>384816</t>
+          <t>406357</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>757150</t>
+          <t>839201</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>757150</t>
+          <t>839201</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>757150</t>
+          <t>839201</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>997657</t>
+          <t>1076428</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>997657</t>
+          <t>1076428</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>997657</t>
+          <t>1076428</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>63949</t>
+          <t>70944</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>46788</t>
+          <t>56757</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>82685</t>
+          <t>89266</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>81909</t>
+          <t>88358</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>66127</t>
+          <t>72927</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>98320</t>
+          <t>105528</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>145858</t>
+          <t>159302</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>121994</t>
+          <t>138343</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>170593</t>
+          <t>182734</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>161512</t>
+          <t>170076</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>119041</t>
+          <t>146542</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>188750</t>
+          <t>195270</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>221500</t>
+          <t>246216</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>177079</t>
+          <t>222127</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>250805</t>
+          <t>273851</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>383011</t>
+          <t>416291</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>330528</t>
+          <t>380217</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>429529</t>
+          <t>452737</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>385854</t>
+          <t>424113</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>292888</t>
+          <t>387271</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>431818</t>
+          <t>466962</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>505129</t>
+          <t>560663</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>411228</t>
+          <t>527499</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>554448</t>
+          <t>602415</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>890983</t>
+          <t>984776</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>780547</t>
+          <t>931368</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>969948</t>
+          <t>1041110</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1433604</t>
+          <t>1555741</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1065398</t>
+          <t>1489032</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1569717</t>
+          <t>1615956</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1682689</t>
+          <t>1606283</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1525327</t>
+          <t>1553016</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>2052009</t>
+          <t>1661453</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>3116294</t>
+          <t>3162024</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2827341</t>
+          <t>3079429</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3464633</t>
+          <t>3243926</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>45,95%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1326475</t>
+          <t>1216804</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1147325</t>
+          <t>1156613</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1873387</t>
+          <t>1285513</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1075418</t>
+          <t>1120143</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>891628</t>
+          <t>1068372</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1227063</t>
+          <t>1175287</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>2401893</t>
+          <t>2336948</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2147257</t>
+          <t>2256815</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2933099</t>
+          <t>2419934</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>34,28%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3371394</t>
+          <t>3437678</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3371394</t>
+          <t>3437678</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3371394</t>
+          <t>3437678</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3566645</t>
+          <t>3621663</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3566645</t>
+          <t>3621663</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3566645</t>
+          <t>3621663</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>6938039</t>
+          <t>7059341</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6938039</t>
+          <t>7059341</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6938039</t>
+          <t>7059341</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
